--- a/SGC-CKN/Excel/15afdbbf-5e8e-4186-8f66-d7fc5038a34a_Cọc_khoan_nhồi_P1-157_D800_26-03-2026.xlsx
+++ b/SGC-CKN/Excel/15afdbbf-5e8e-4186-8f66-d7fc5038a34a_Cọc_khoan_nhồi_P1-157_D800_26-03-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>P1-157</t>
+    <t>P1-137</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>

--- a/SGC-CKN/Excel/15afdbbf-5e8e-4186-8f66-d7fc5038a34a_Cọc_khoan_nhồi_P1-157_D800_26-03-2026.xlsx
+++ b/SGC-CKN/Excel/15afdbbf-5e8e-4186-8f66-d7fc5038a34a_Cọc_khoan_nhồi_P1-157_D800_26-03-2026.xlsx
@@ -59,7 +59,7 @@
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>11:31 26/03/2026</t>
+    <t>11:31 25/03/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -98,11 +98,11 @@
     <t>Đất thổ nhưỡng</t>
   </si>
   <si>
-    <t xml:space="preserve">14:45
+    <t xml:space="preserve">01:45
 25/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">21:55
+    <t xml:space="preserve">01:55
 25/03/2026</t>
   </si>
   <si>
@@ -217,7 +217,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -248,8 +248,7 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFC2410C"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
@@ -260,11 +259,6 @@
     </font>
     <font>
       <color rgb="FF065F46"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color rgb="FFC2410C"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
@@ -306,7 +300,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -335,7 +329,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC2626"/>
+        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -361,11 +355,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDD6FE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -476,7 +465,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -520,29 +509,35 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -562,22 +557,13 @@
     <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1169,13 +1155,13 @@
         <v>-1.85</v>
       </c>
       <c r="H11" s="5">
-        <v>7.17</v>
+        <v>0.17</v>
       </c>
       <c r="I11" s="5">
         <v>1.85</v>
       </c>
       <c r="J11" s="8">
-        <v>0.26</v>
+        <v>11.1</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1204,13 +1190,13 @@
         <v>-4.95</v>
       </c>
       <c r="H12" s="9">
-        <v>4.42</v>
+        <v>0.42</v>
       </c>
       <c r="I12" s="9">
         <v>3.1</v>
       </c>
       <c r="J12" s="8">
-        <v>0.7</v>
+        <v>7.44</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>30</v>
@@ -1271,16 +1257,16 @@
         <v>-8.25</v>
       </c>
       <c r="G14" s="16">
-        <v>-12.05</v>
+        <v>-17.05</v>
       </c>
       <c r="H14" s="16">
         <v>1.58</v>
       </c>
       <c r="I14" s="16">
-        <v>3.8</v>
-      </c>
-      <c r="J14" s="15">
-        <v>2.4</v>
+        <v>8.8</v>
+      </c>
+      <c r="J14" s="8">
+        <v>5.56</v>
       </c>
       <c r="K14" s="17" t="s">
         <v>30</v>
@@ -1303,143 +1289,143 @@
         <v>42</v>
       </c>
       <c r="F15" s="19">
-        <v>-12.05</v>
+        <v>-17.05</v>
       </c>
       <c r="G15" s="19">
-        <v>-22.15</v>
+        <v>-22.25</v>
       </c>
       <c r="H15" s="19">
         <v>0.83</v>
       </c>
       <c r="I15" s="19">
-        <v>10.1</v>
-      </c>
-      <c r="J15" s="22">
-        <v>12.12</v>
+        <v>5.2</v>
+      </c>
+      <c r="J15" s="8">
+        <v>6.24</v>
       </c>
       <c r="K15" s="20" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="24" t="s">
+      <c r="C16" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="25" t="s">
+      <c r="D16" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="E16" s="25" t="s">
+      <c r="E16" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="F16" s="23">
-        <v>-22.15</v>
-      </c>
-      <c r="G16" s="23">
+      <c r="F16" s="22">
+        <v>-22.25</v>
+      </c>
+      <c r="G16" s="22">
         <v>-26.25</v>
       </c>
-      <c r="H16" s="23">
+      <c r="H16" s="22">
         <v>0.58</v>
       </c>
-      <c r="I16" s="23">
-        <v>4.1</v>
-      </c>
-      <c r="J16" s="22">
-        <v>7.03</v>
-      </c>
-      <c r="K16" s="24" t="s">
+      <c r="I16" s="22">
+        <v>4</v>
+      </c>
+      <c r="J16" s="8">
+        <v>6.86</v>
+      </c>
+      <c r="K16" s="23" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="26" t="s">
+      <c r="B17" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="27" t="s">
+      <c r="C17" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="D17" s="28" t="s">
+      <c r="D17" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="E17" s="28" t="s">
+      <c r="E17" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="F17" s="26">
+      <c r="F17" s="25">
         <v>-26.25</v>
       </c>
-      <c r="G17" s="26">
+      <c r="G17" s="25">
         <v>-39.5</v>
       </c>
-      <c r="H17" s="26">
+      <c r="H17" s="25">
         <v>3.55</v>
       </c>
-      <c r="I17" s="26">
+      <c r="I17" s="25">
         <v>13.25</v>
       </c>
       <c r="J17" s="15">
         <v>3.73</v>
       </c>
-      <c r="K17" s="27" t="s">
+      <c r="K17" s="26" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="B18" s="29" t="s">
+      <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="30" t="s">
+      <c r="C18" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="D18" s="31" t="s">
+      <c r="D18" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="E18" s="31" t="s">
+      <c r="E18" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="28">
         <v>-39.5</v>
       </c>
-      <c r="G18" s="29">
+      <c r="G18" s="28">
         <v>-44.33</v>
       </c>
-      <c r="H18" s="29">
+      <c r="H18" s="28">
         <v>0.97</v>
       </c>
-      <c r="I18" s="29">
+      <c r="I18" s="28">
         <v>4.83</v>
       </c>
       <c r="J18" s="15">
         <v>5</v>
       </c>
-      <c r="K18" s="30" t="s">
+      <c r="K18" s="29" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="32" t="s">
+      <c r="A21" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="B21" s="32"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
-      <c r="K21" s="32"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
     </row>
     <row r="22" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1581,13 +1567,13 @@
         <v>-1.85</v>
       </c>
       <c r="G2" s="5">
-        <v>7.17</v>
+        <v>0.17</v>
       </c>
       <c r="H2" s="5">
         <v>1.85</v>
       </c>
       <c r="I2" s="8">
-        <v>0.26</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1610,13 +1596,13 @@
         <v>-4.95</v>
       </c>
       <c r="G3" s="9">
-        <v>4.42</v>
+        <v>0.42</v>
       </c>
       <c r="H3" s="9">
         <v>3.1</v>
       </c>
       <c r="I3" s="8">
-        <v>0.7</v>
+        <v>7.44</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1665,16 +1651,16 @@
         <v>-8.25</v>
       </c>
       <c r="F5" s="16">
-        <v>-12.05</v>
+        <v>-17.05</v>
       </c>
       <c r="G5" s="16">
         <v>1.58</v>
       </c>
       <c r="H5" s="16">
-        <v>3.8</v>
-      </c>
-      <c r="I5" s="15">
-        <v>2.4</v>
+        <v>8.8</v>
+      </c>
+      <c r="I5" s="8">
+        <v>5.56</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1691,73 +1677,73 @@
         <v>1</v>
       </c>
       <c r="E6" s="19">
-        <v>-12.05</v>
+        <v>-17.05</v>
       </c>
       <c r="F6" s="19">
-        <v>-22.15</v>
+        <v>-22.25</v>
       </c>
       <c r="G6" s="19">
         <v>0.83</v>
       </c>
       <c r="H6" s="19">
-        <v>10.1</v>
-      </c>
-      <c r="I6" s="22">
-        <v>12.12</v>
+        <v>5.2</v>
+      </c>
+      <c r="I6" s="8">
+        <v>6.24</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="23">
+      <c r="A7" s="22">
         <v>6</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="22">
         <v>1</v>
       </c>
-      <c r="E7" s="23">
-        <v>-22.15</v>
-      </c>
-      <c r="F7" s="23">
+      <c r="E7" s="22">
+        <v>-22.25</v>
+      </c>
+      <c r="F7" s="22">
         <v>-26.25</v>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="22">
         <v>0.58</v>
       </c>
-      <c r="H7" s="23">
-        <v>4.1</v>
-      </c>
-      <c r="I7" s="22">
-        <v>7.03</v>
+      <c r="H7" s="22">
+        <v>4</v>
+      </c>
+      <c r="I7" s="8">
+        <v>6.86</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="26">
+      <c r="A8" s="25">
         <v>7</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="27" t="s">
+      <c r="C8" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="25">
         <v>1</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="25">
         <v>-26.25</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="25">
         <v>-39.5</v>
       </c>
-      <c r="G8" s="26">
+      <c r="G8" s="25">
         <v>3.55</v>
       </c>
-      <c r="H8" s="26">
+      <c r="H8" s="25">
         <v>13.25</v>
       </c>
       <c r="I8" s="15">
@@ -1765,28 +1751,28 @@
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="29">
+      <c r="A9" s="28">
         <v>8</v>
       </c>
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="30" t="s">
+      <c r="C9" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="28">
         <v>1</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="28">
         <v>-39.5</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="28">
         <v>-44.33</v>
       </c>
-      <c r="G9" s="29">
+      <c r="G9" s="28">
         <v>0.97</v>
       </c>
-      <c r="H9" s="29">
+      <c r="H9" s="28">
         <v>4.83</v>
       </c>
       <c r="I9" s="15">
@@ -1794,32 +1780,32 @@
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="33" t="s">
+      <c r="A10" s="32" t="s">
         <v>62</v>
       </c>
-      <c r="B10" s="34" t="s">
+      <c r="B10" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="34">
+      <c r="D10" s="33">
         <v>8</v>
       </c>
-      <c r="E10" s="34">
+      <c r="E10" s="33">
         <v>0</v>
       </c>
-      <c r="F10" s="34">
+      <c r="F10" s="33">
         <v>-44.33</v>
       </c>
-      <c r="G10" s="34">
-        <v>20.02</v>
-      </c>
-      <c r="H10" s="34">
+      <c r="G10" s="33">
+        <v>9.02</v>
+      </c>
+      <c r="H10" s="33">
         <v>44.33</v>
       </c>
-      <c r="I10" s="34">
-        <v>2.21</v>
+      <c r="I10" s="33">
+        <v>4.92</v>
       </c>
     </row>
   </sheetData>
